--- a/cet4/result/59_重生女帝_凤凰涅槃的崛起路/59_重生女帝_凤凰涅槃的崛起路_学习版.xlsx
+++ b/cet4/result/59_重生女帝_凤凰涅槃的崛起路/59_重生女帝_凤凰涅槃的崛起路_学习版.xlsx
@@ -397,717 +397,675 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D47"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>dusk</v>
       </c>
       <c r="B2" t="str">
-        <v>dusk</v>
+        <v>/dʌsk/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>黄昏</v>
       </c>
-      <c r="D2" t="str">
-        <v>dusk(黄昏)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>vast</v>
       </c>
       <c r="B3" t="str">
-        <v>vast</v>
+        <v>/væst/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>广阔的</v>
       </c>
-      <c r="D3" t="str">
-        <v>vast(广阔的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>graduate</v>
       </c>
       <c r="B4" t="str">
-        <v>graduate</v>
+        <v>/ˈɡrædʒuət/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D4" t="str">
         <v>大学毕业生</v>
       </c>
-      <c r="D4" t="str">
-        <v>graduate(大学毕业生)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>slavery</v>
       </c>
       <c r="B5" t="str">
-        <v>slavery</v>
+        <v>/ˈsleɪvəri/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>奴役</v>
       </c>
-      <c r="D5" t="str">
-        <v>slavery(奴役)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>vegetable</v>
       </c>
       <c r="B6" t="str">
-        <v>vegetable</v>
+        <v>/ˈvedʒtəbl/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>蔬菜</v>
       </c>
-      <c r="D6" t="str">
-        <v>vegetable(蔬菜)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>bean</v>
       </c>
       <c r="B7" t="str">
-        <v>bean</v>
+        <v>/biːn/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D7" t="str">
         <v>豆类</v>
       </c>
-      <c r="D7" t="str">
-        <v>bean(豆类)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>fate</v>
       </c>
       <c r="B8" t="str">
-        <v>fate</v>
+        <v>/feɪt/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D8" t="str">
         <v>命运</v>
       </c>
-      <c r="D8" t="str">
-        <v>fate(命运)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>apply</v>
       </c>
       <c r="B9" t="str">
-        <v>apply</v>
+        <v>/əˈplaɪ/</v>
       </c>
       <c r="C9" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>应用</v>
       </c>
-      <c r="D9" t="str">
-        <v>apply(应用)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>quality</v>
       </c>
       <c r="B10" t="str">
-        <v>quality</v>
+        <v>/ˈkwɑːləti/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>质量</v>
       </c>
-      <c r="D10" t="str">
-        <v>quality(质量)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>respect</v>
       </c>
       <c r="B11" t="str">
-        <v>respect</v>
+        <v>/rɪˈspekt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>尊重</v>
       </c>
-      <c r="D11" t="str">
-        <v>respect(尊重)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>boss</v>
       </c>
       <c r="B12" t="str">
-        <v>boss</v>
+        <v>/bɔːs/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>首领</v>
       </c>
-      <c r="D12" t="str">
-        <v>boss(首领)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>premier</v>
       </c>
       <c r="B13" t="str">
-        <v>premier</v>
+        <v>/prɪˈmɪr,prɪˈmjɪr/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>首相</v>
       </c>
-      <c r="D13" t="str">
-        <v>premier(首相)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>head</v>
       </c>
       <c r="B14" t="str">
-        <v>head</v>
+        <v>/hed/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>首领</v>
       </c>
-      <c r="D14" t="str">
-        <v>head(首领)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>seriously</v>
       </c>
       <c r="B15" t="str">
-        <v>seriously</v>
+        <v>/ˈsɪriəsli/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D15" t="str">
         <v>认真地</v>
       </c>
-      <c r="D15" t="str">
-        <v>seriously(认真地)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>revolt</v>
       </c>
       <c r="B16" t="str">
-        <v>revolt</v>
+        <v>/rɪˈvoʊlt/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D16" t="str">
         <v>叛乱</v>
       </c>
-      <c r="D16" t="str">
-        <v>revolt(叛乱)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>retreat</v>
       </c>
       <c r="B17" t="str">
-        <v>retreat</v>
+        <v>/rɪˈtriːt/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>撤退</v>
       </c>
-      <c r="D17" t="str">
-        <v>retreat(撤退)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>candy</v>
       </c>
       <c r="B18" t="str">
-        <v>candy</v>
+        <v>/ˈkændi/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D18" t="str">
         <v>糖果</v>
       </c>
-      <c r="D18" t="str">
-        <v>candy(糖果)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>conquer</v>
       </c>
       <c r="B19" t="str">
-        <v>conquer</v>
+        <v>/ˈkɑːŋkər/</v>
       </c>
       <c r="C19" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>征服</v>
       </c>
-      <c r="D19" t="str">
-        <v>conquer(征服)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>bomb</v>
       </c>
       <c r="B20" t="str">
-        <v>bomb</v>
+        <v>/bɑːm/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D20" t="str">
         <v>炸弹</v>
       </c>
-      <c r="D20" t="str">
-        <v>bomb(炸弹)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>stone</v>
       </c>
       <c r="B21" t="str">
-        <v>stone</v>
+        <v>/stoʊn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>石头</v>
       </c>
-      <c r="D21" t="str">
-        <v>stone(石头)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>greatly</v>
       </c>
       <c r="B22" t="str">
-        <v>greatly</v>
+        <v>/ˈɡreɪtli/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D22" t="str">
         <v>大大地</v>
       </c>
-      <c r="D22" t="str">
-        <v>greatly(大大地)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>standpoint</v>
       </c>
       <c r="B23" t="str">
-        <v>standpoint</v>
+        <v>/ˈstændpɔɪnt/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>立场</v>
       </c>
-      <c r="D23" t="str">
-        <v>standpoint(立场)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>prohibit</v>
       </c>
       <c r="B24" t="str">
-        <v>prohibit</v>
+        <v>/prəˈhɪbɪt,proʊˈhɪbɪt/</v>
       </c>
       <c r="C24" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D24" t="str">
         <v>禁止</v>
       </c>
-      <c r="D24" t="str">
-        <v>prohibit(禁止)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>daily</v>
       </c>
       <c r="B25" t="str">
-        <v>daily</v>
+        <v>/ˈdeɪli/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D25" t="str">
         <v>日常的</v>
       </c>
-      <c r="D25" t="str">
-        <v>daily(日常的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>size</v>
       </c>
       <c r="B26" t="str">
-        <v>size</v>
+        <v>/saɪz/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>规模</v>
       </c>
-      <c r="D26" t="str">
-        <v>size(规模)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>dirty</v>
       </c>
       <c r="B27" t="str">
-        <v>dirty</v>
+        <v>/ˈdɜːrti/</v>
       </c>
       <c r="C27" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>肮脏的</v>
       </c>
-      <c r="D27" t="str">
-        <v>dirty(肮脏的)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>tax</v>
       </c>
       <c r="B28" t="str">
-        <v>tax</v>
+        <v>/tæks/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D28" t="str">
         <v>税收</v>
       </c>
-      <c r="D28" t="str">
-        <v>tax(税收)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>professor</v>
       </c>
       <c r="B29" t="str">
-        <v>professor</v>
+        <v>/prəˈfesər/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>教授</v>
       </c>
-      <c r="D29" t="str">
-        <v>professor(教授)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>renew</v>
       </c>
       <c r="B30" t="str">
-        <v>renew</v>
+        <v>/rɪˈnuː/</v>
       </c>
       <c r="C30" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D30" t="str">
         <v>复兴</v>
       </c>
-      <c r="D30" t="str">
-        <v>renew(复兴)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>knit</v>
       </c>
       <c r="B31" t="str">
-        <v>knit</v>
+        <v>/nɪt/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>编织</v>
       </c>
-      <c r="D31" t="str">
-        <v>knit(编织)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>irregular</v>
       </c>
       <c r="B32" t="str">
-        <v>irregular</v>
+        <v>/ɪˈreɡjələr/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>非正规的</v>
       </c>
-      <c r="D32" t="str">
-        <v>irregular(非正规的)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>justify</v>
       </c>
       <c r="B33" t="str">
-        <v>justify</v>
+        <v>/ˈdʒʌstɪfaɪ/</v>
       </c>
       <c r="C33" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D33" t="str">
         <v>证明</v>
       </c>
-      <c r="D33" t="str">
-        <v>justify(证明)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>distribute</v>
       </c>
       <c r="B34" t="str">
-        <v>slavery</v>
+        <v>/dɪˈstrɪbjuːt/</v>
       </c>
       <c r="C34" t="str">
-        <v>奴隶制度</v>
+        <v>vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>slavery(奴隶制度)📢</v>
+        <v>分配</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>attempt</v>
       </c>
       <c r="B35" t="str">
-        <v>distribute</v>
+        <v>/əˈtempt/</v>
       </c>
       <c r="C35" t="str">
-        <v>分配</v>
+        <v>n./vt.</v>
       </c>
       <c r="D35" t="str">
-        <v>distribute(分配)📢</v>
+        <v>企图</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>weld</v>
       </c>
       <c r="B36" t="str">
-        <v>attempt</v>
+        <v>/weld/</v>
       </c>
       <c r="C36" t="str">
-        <v>企图</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>attempt(企图)📢</v>
+        <v>结合</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>habit</v>
       </c>
       <c r="B37" t="str">
-        <v>weld</v>
+        <v>/ˈhæbɪt/</v>
       </c>
       <c r="C37" t="str">
-        <v>结合</v>
+        <v>n./vt.</v>
       </c>
       <c r="D37" t="str">
-        <v>weld(结合)📢</v>
+        <v>习惯</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>graph</v>
       </c>
       <c r="B38" t="str">
-        <v>habit</v>
+        <v>/ɡræf/</v>
       </c>
       <c r="C38" t="str">
-        <v>习惯</v>
+        <v>n./vt.</v>
       </c>
       <c r="D38" t="str">
-        <v>habit(习惯)📢</v>
+        <v>图表</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>till</v>
       </c>
       <c r="B39" t="str">
-        <v>graph</v>
+        <v>/tɪl/</v>
       </c>
       <c r="C39" t="str">
-        <v>图表</v>
+        <v>n./vt./prep./conj.</v>
       </c>
       <c r="D39" t="str">
-        <v>graph(图表)📢</v>
+        <v>直到</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>guide</v>
       </c>
       <c r="B40" t="str">
-        <v>daily</v>
+        <v>/ɡaɪd/</v>
       </c>
       <c r="C40" t="str">
-        <v>日常的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>daily(日常的)📢</v>
+        <v>指南</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>mend</v>
       </c>
       <c r="B41" t="str">
-        <v>till</v>
+        <v>/mend/</v>
       </c>
       <c r="C41" t="str">
-        <v>直到</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>till(直到)📢</v>
+        <v>修补</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>hare</v>
       </c>
       <c r="B42" t="str">
-        <v>guide</v>
+        <v>/her/</v>
       </c>
       <c r="C42" t="str">
-        <v>指南</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>guide(指南)📢</v>
+        <v>野兔</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>silver</v>
       </c>
       <c r="B43" t="str">
-        <v>fate</v>
+        <v>/ˈsɪlvər/</v>
       </c>
       <c r="C43" t="str">
-        <v>命运</v>
+        <v>n./vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>fate(命运)📢</v>
+        <v>银色</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>stir</v>
       </c>
       <c r="B44" t="str">
-        <v>mend</v>
+        <v>/stɜːr/</v>
       </c>
       <c r="C44" t="str">
-        <v>修补</v>
+        <v>n./v.</v>
       </c>
       <c r="D44" t="str">
-        <v>mend(修补)📢</v>
+        <v>搅动</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>safely</v>
       </c>
       <c r="B45" t="str">
-        <v>hare</v>
+        <v>/ˈseɪfli/</v>
       </c>
       <c r="C45" t="str">
-        <v>野兔</v>
+        <v>v./adv.</v>
       </c>
       <c r="D45" t="str">
-        <v>hare(野兔)📢</v>
+        <v>安全地</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>flare</v>
       </c>
       <c r="B46" t="str">
-        <v>silver</v>
+        <v>/fler/</v>
       </c>
       <c r="C46" t="str">
-        <v>银色</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>silver(银色)📢</v>
+        <v>闪耀</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>preceding</v>
       </c>
       <c r="B47" t="str">
-        <v>stir</v>
+        <v>/prɪˈsiːdɪŋ/</v>
       </c>
       <c r="C47" t="str">
-        <v>搅动</v>
+        <v>v./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>stir(搅动)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>safely</v>
-      </c>
-      <c r="C48" t="str">
-        <v>安全地</v>
-      </c>
-      <c r="D48" t="str">
-        <v>safely(安全地)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>flare</v>
-      </c>
-      <c r="C49" t="str">
-        <v>闪耀</v>
-      </c>
-      <c r="D49" t="str">
-        <v>flare(闪耀)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>preceding</v>
-      </c>
-      <c r="C50" t="str">
         <v>先前的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>preceding(先前的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D47"/>
   </ignoredErrors>
 </worksheet>
 </file>